--- a/filer/38454218_ege.xlsx
+++ b/filer/38454218_ege.xlsx
@@ -7506,7 +7506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7764,28 +7764,28 @@
       </c>
       <c r="B9" s="34" t="inlineStr">
         <is>
-          <t>fsa:IncreaseDecreaseOfInvestmentsThroughNetExchangeDifferencesEquity</t>
+          <t>fsa:LongtermTaxPayables</t>
         </is>
       </c>
       <c r="C9" s="34" t="inlineStr">
         <is>
-          <t>fsa:IncreaseDecreaseOfInvestmentsThroughNetExchangeDifferencesEquity</t>
+          <t>fsa:LongtermTaxPayables</t>
         </is>
       </c>
       <c r="D9" s="35" t="n">
-        <v>-2210</v>
+        <v>30705</v>
       </c>
       <c r="E9" s="35" t="n">
-        <v>-727</v>
+        <v>30518</v>
       </c>
       <c r="F9" s="35" t="n">
-        <v>3063</v>
+        <v>34878</v>
       </c>
       <c r="G9" s="35" t="n">
-        <v>4200</v>
+        <v>34460</v>
       </c>
       <c r="H9" s="35" t="n">
-        <v>-1080</v>
+        <v>34722</v>
       </c>
       <c r="I9" s="36" t="inlineStr">
         <is>
@@ -7801,29 +7801,19 @@
       </c>
       <c r="B10" s="37" t="inlineStr">
         <is>
-          <t>fsa:LongtermTaxPayables</t>
+          <t>fsa:PurchaseOfMinorityShares</t>
         </is>
       </c>
       <c r="C10" s="37" t="inlineStr">
         <is>
-          <t>fsa:LongtermTaxPayables</t>
-        </is>
-      </c>
-      <c r="D10" s="38" t="n">
-        <v>30705</v>
-      </c>
-      <c r="E10" s="38" t="n">
-        <v>30518</v>
-      </c>
-      <c r="F10" s="38" t="n">
-        <v>34878</v>
-      </c>
-      <c r="G10" s="38" t="n">
-        <v>34460</v>
-      </c>
-      <c r="H10" s="38" t="n">
-        <v>34722</v>
-      </c>
+          <t>fsa:PurchaseOfMinorityShares</t>
+        </is>
+      </c>
+      <c r="D10" s="38" t="n"/>
+      <c r="E10" s="38" t="n"/>
+      <c r="F10" s="38" t="n"/>
+      <c r="G10" s="38" t="n"/>
+      <c r="H10" s="38" t="n"/>
       <c r="I10" s="39" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -7838,21 +7828,23 @@
       </c>
       <c r="B11" s="34" t="inlineStr">
         <is>
-          <t>fsa:ProfitLossFromOrdinaryActivitiesAfterTax</t>
+          <t>fsa:RaisingOfLongtermDebt</t>
         </is>
       </c>
       <c r="C11" s="34" t="inlineStr">
         <is>
-          <t>fsa:ProfitLossFromOrdinaryActivitiesAfterTax</t>
+          <t>fsa:RaisingOfLongtermDebt</t>
         </is>
       </c>
       <c r="D11" s="35" t="n">
-        <v>566</v>
+        <v>57691</v>
       </c>
       <c r="E11" s="35" t="n">
-        <v>-2418</v>
-      </c>
-      <c r="F11" s="35" t="n"/>
+        <v>26004</v>
+      </c>
+      <c r="F11" s="35" t="n">
+        <v>0</v>
+      </c>
       <c r="G11" s="35" t="n"/>
       <c r="H11" s="35" t="n"/>
       <c r="I11" s="36" t="inlineStr">
@@ -7869,17 +7861,19 @@
       </c>
       <c r="B12" s="37" t="inlineStr">
         <is>
-          <t>fsa:PurchaseOfMinorityShares</t>
+          <t>fsa:ShorttermPayablesToAssociates</t>
         </is>
       </c>
       <c r="C12" s="37" t="inlineStr">
         <is>
-          <t>fsa:PurchaseOfMinorityShares</t>
+          <t>fsa:ShorttermPayablesToAssociates</t>
         </is>
       </c>
       <c r="D12" s="38" t="n"/>
       <c r="E12" s="38" t="n"/>
-      <c r="F12" s="38" t="n"/>
+      <c r="F12" s="38" t="n">
+        <v>136858</v>
+      </c>
       <c r="G12" s="38" t="n"/>
       <c r="H12" s="38" t="n"/>
       <c r="I12" s="39" t="inlineStr">
@@ -7896,24 +7890,26 @@
       </c>
       <c r="B13" s="34" t="inlineStr">
         <is>
-          <t>fsa:RaisingOfLongtermDebt</t>
+          <t>fsa:ShorttermPayablesToJointVentures</t>
         </is>
       </c>
       <c r="C13" s="34" t="inlineStr">
         <is>
-          <t>fsa:RaisingOfLongtermDebt</t>
+          <t>fsa:ShorttermPayablesToJointVentures</t>
         </is>
       </c>
       <c r="D13" s="35" t="n">
-        <v>57691</v>
+        <v>1833</v>
       </c>
       <c r="E13" s="35" t="n">
-        <v>26004</v>
+        <v>2222</v>
       </c>
       <c r="F13" s="35" t="n">
+        <v>1307</v>
+      </c>
+      <c r="G13" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="G13" s="35" t="n"/>
       <c r="H13" s="35" t="n"/>
       <c r="I13" s="36" t="inlineStr">
         <is>
@@ -7929,21 +7925,23 @@
       </c>
       <c r="B14" s="37" t="inlineStr">
         <is>
-          <t>fsa:ShorttermPayablesToAssociates</t>
+          <t>fsa:ShorttermPayablesToParticipatingInterest</t>
         </is>
       </c>
       <c r="C14" s="37" t="inlineStr">
         <is>
-          <t>fsa:ShorttermPayablesToAssociates</t>
+          <t>fsa:ShorttermPayablesToParticipatingInterest</t>
         </is>
       </c>
       <c r="D14" s="38" t="n"/>
       <c r="E14" s="38" t="n"/>
-      <c r="F14" s="38" t="n">
-        <v>136858</v>
-      </c>
-      <c r="G14" s="38" t="n"/>
-      <c r="H14" s="38" t="n"/>
+      <c r="F14" s="38" t="n"/>
+      <c r="G14" s="38" t="n">
+        <v>2952</v>
+      </c>
+      <c r="H14" s="38" t="n">
+        <v>0</v>
+      </c>
       <c r="I14" s="39" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -7958,26 +7956,18 @@
       </c>
       <c r="B15" s="34" t="inlineStr">
         <is>
-          <t>fsa:ShorttermPayablesToJointVentures</t>
+          <t>fsa:ShorttermReceivablesFromOwnersAndManagement</t>
         </is>
       </c>
       <c r="C15" s="34" t="inlineStr">
         <is>
-          <t>fsa:ShorttermPayablesToJointVentures</t>
-        </is>
-      </c>
-      <c r="D15" s="35" t="n">
-        <v>1833</v>
-      </c>
-      <c r="E15" s="35" t="n">
-        <v>2222</v>
-      </c>
-      <c r="F15" s="35" t="n">
-        <v>1307</v>
-      </c>
-      <c r="G15" s="35" t="n">
-        <v>0</v>
-      </c>
+          <t>fsa:ShorttermReceivablesFromOwnersAndManagement</t>
+        </is>
+      </c>
+      <c r="D15" s="35" t="n"/>
+      <c r="E15" s="35" t="n"/>
+      <c r="F15" s="35" t="n"/>
+      <c r="G15" s="35" t="n"/>
       <c r="H15" s="35" t="n"/>
       <c r="I15" s="36" t="inlineStr">
         <is>
@@ -7993,80 +7983,22 @@
       </c>
       <c r="B16" s="37" t="inlineStr">
         <is>
-          <t>fsa:ShorttermPayablesToParticipatingInterest</t>
+          <t>fsa:TrademarksOriginatingFromDevelopmentProjects</t>
         </is>
       </c>
       <c r="C16" s="37" t="inlineStr">
         <is>
-          <t>fsa:ShorttermPayablesToParticipatingInterest</t>
+          <t>fsa:TrademarksOriginatingFromDevelopmentProjects</t>
         </is>
       </c>
       <c r="D16" s="38" t="n"/>
       <c r="E16" s="38" t="n"/>
-      <c r="F16" s="38" t="n"/>
-      <c r="G16" s="38" t="n">
-        <v>2952</v>
-      </c>
-      <c r="H16" s="38" t="n">
-        <v>0</v>
-      </c>
+      <c r="F16" s="38" t="n">
+        <v>2181</v>
+      </c>
+      <c r="G16" s="38" t="n"/>
+      <c r="H16" s="38" t="n"/>
       <c r="I16" s="39" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="34" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B17" s="34" t="inlineStr">
-        <is>
-          <t>fsa:ShorttermReceivablesFromOwnersAndManagement</t>
-        </is>
-      </c>
-      <c r="C17" s="34" t="inlineStr">
-        <is>
-          <t>fsa:ShorttermReceivablesFromOwnersAndManagement</t>
-        </is>
-      </c>
-      <c r="D17" s="35" t="n"/>
-      <c r="E17" s="35" t="n"/>
-      <c r="F17" s="35" t="n"/>
-      <c r="G17" s="35" t="n"/>
-      <c r="H17" s="35" t="n"/>
-      <c r="I17" s="36" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="37" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B18" s="37" t="inlineStr">
-        <is>
-          <t>fsa:TrademarksOriginatingFromDevelopmentProjects</t>
-        </is>
-      </c>
-      <c r="C18" s="37" t="inlineStr">
-        <is>
-          <t>fsa:TrademarksOriginatingFromDevelopmentProjects</t>
-        </is>
-      </c>
-      <c r="D18" s="38" t="n"/>
-      <c r="E18" s="38" t="n"/>
-      <c r="F18" s="38" t="n">
-        <v>2181</v>
-      </c>
-      <c r="G18" s="38" t="n"/>
-      <c r="H18" s="38" t="n"/>
-      <c r="I18" s="39" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
         </is>

--- a/filer/38454218_ege.xlsx
+++ b/filer/38454218_ege.xlsx
@@ -648,7 +648,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.)</t>
+          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.) · Klasse C-stor · Revision · Regnskabsår 1/5–30/4 (forskudt)</t>
         </is>
       </c>
     </row>

--- a/filer/38454218_ege.xlsx
+++ b/filer/38454218_ege.xlsx
@@ -10,8 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overblik_38454218" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="res_raw_38454218" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="balance_raw_38454218" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simpel_arts" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Noter_info" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pengestrom_raw_38454218" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simpel_arts" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Noter_info" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -204,9 +205,9 @@
     <xf numFmtId="164" fontId="3" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -628,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L97"/>
+  <dimension ref="A1:L104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -4722,6 +4723,148 @@
       </c>
       <c r="F97" s="13">
         <f>IFERROR($F$36/($F$61+$F$66)*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="15" t="inlineStr">
+        <is>
+          <t>PENGESTRØMSOPGØRELSE t.kr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra driftsaktivitet</t>
+        </is>
+      </c>
+      <c r="B100" s="17">
+        <f>'pengestrom_raw_38454218'!$B$2</f>
+        <v/>
+      </c>
+      <c r="C100" s="17">
+        <f>'pengestrom_raw_38454218'!$C$2</f>
+        <v/>
+      </c>
+      <c r="D100" s="17">
+        <f>'pengestrom_raw_38454218'!$D$2</f>
+        <v/>
+      </c>
+      <c r="E100" s="17">
+        <f>'pengestrom_raw_38454218'!$E$2</f>
+        <v/>
+      </c>
+      <c r="F100" s="17">
+        <f>'pengestrom_raw_38454218'!$F$2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra investeringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B101" s="17">
+        <f>'pengestrom_raw_38454218'!$B$3</f>
+        <v/>
+      </c>
+      <c r="C101" s="17">
+        <f>'pengestrom_raw_38454218'!$C$3</f>
+        <v/>
+      </c>
+      <c r="D101" s="17">
+        <f>'pengestrom_raw_38454218'!$D$3</f>
+        <v/>
+      </c>
+      <c r="E101" s="17">
+        <f>'pengestrom_raw_38454218'!$E$3</f>
+        <v/>
+      </c>
+      <c r="F101" s="17">
+        <f>'pengestrom_raw_38454218'!$F$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra finansieringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B102" s="17">
+        <f>'pengestrom_raw_38454218'!$B$4</f>
+        <v/>
+      </c>
+      <c r="C102" s="17">
+        <f>'pengestrom_raw_38454218'!$C$4</f>
+        <v/>
+      </c>
+      <c r="D102" s="17">
+        <f>'pengestrom_raw_38454218'!$D$4</f>
+        <v/>
+      </c>
+      <c r="E102" s="17">
+        <f>'pengestrom_raw_38454218'!$E$4</f>
+        <v/>
+      </c>
+      <c r="F102" s="17">
+        <f>'pengestrom_raw_38454218'!$F$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="16" t="inlineStr">
+        <is>
+          <t>Årets pengestrøm (rapporteret)</t>
+        </is>
+      </c>
+      <c r="B103" s="17">
+        <f>'pengestrom_raw_38454218'!$B$5</f>
+        <v/>
+      </c>
+      <c r="C103" s="17">
+        <f>'pengestrom_raw_38454218'!$C$5</f>
+        <v/>
+      </c>
+      <c r="D103" s="17">
+        <f>'pengestrom_raw_38454218'!$D$5</f>
+        <v/>
+      </c>
+      <c r="E103" s="17">
+        <f>'pengestrom_raw_38454218'!$E$5</f>
+        <v/>
+      </c>
+      <c r="F103" s="17">
+        <f>'pengestrom_raw_38454218'!$F$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="16" t="inlineStr">
+        <is>
+          <t>Krydstjek: drift + inv. + fin. = årets pengestrøm</t>
+        </is>
+      </c>
+      <c r="B104">
+        <f>IF(ABS(('pengestrom_raw_38454218'!$B$2+'pengestrom_raw_38454218'!$B$3+'pengestrom_raw_38454218'!$B$4)-'pengestrom_raw_38454218'!$B$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_38454218'!$B$2+'pengestrom_raw_38454218'!$B$3+'pengestrom_raw_38454218'!$B$4)-'pengestrom_raw_38454218'!$B$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="C104">
+        <f>IF(ABS(('pengestrom_raw_38454218'!$C$2+'pengestrom_raw_38454218'!$C$3+'pengestrom_raw_38454218'!$C$4)-'pengestrom_raw_38454218'!$C$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_38454218'!$C$2+'pengestrom_raw_38454218'!$C$3+'pengestrom_raw_38454218'!$C$4)-'pengestrom_raw_38454218'!$C$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="D104">
+        <f>IF(ABS(('pengestrom_raw_38454218'!$D$2+'pengestrom_raw_38454218'!$D$3+'pengestrom_raw_38454218'!$D$4)-'pengestrom_raw_38454218'!$D$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_38454218'!$D$2+'pengestrom_raw_38454218'!$D$3+'pengestrom_raw_38454218'!$D$4)-'pengestrom_raw_38454218'!$D$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="E104">
+        <f>IF(ABS(('pengestrom_raw_38454218'!$E$2+'pengestrom_raw_38454218'!$E$3+'pengestrom_raw_38454218'!$E$4)-'pengestrom_raw_38454218'!$E$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_38454218'!$E$2+'pengestrom_raw_38454218'!$E$3+'pengestrom_raw_38454218'!$E$4)-'pengestrom_raw_38454218'!$E$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="F104">
+        <f>IF(ABS(('pengestrom_raw_38454218'!$F$2+'pengestrom_raw_38454218'!$F$3+'pengestrom_raw_38454218'!$F$4)-'pengestrom_raw_38454218'!$F$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_38454218'!$F$2+'pengestrom_raw_38454218'!$F$3+'pengestrom_raw_38454218'!$F$4)-'pengestrom_raw_38454218'!$F$5,"+#,##0;-#,##0"))</f>
         <v/>
       </c>
     </row>
@@ -4770,393 +4913,393 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Nettoomsætning</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n">
+      <c r="B2" s="17" t="n">
         <v>914782</v>
       </c>
-      <c r="C2" s="16" t="n">
+      <c r="C2" s="17" t="n">
         <v>1085311</v>
       </c>
-      <c r="D2" s="16" t="n">
+      <c r="D2" s="17" t="n">
         <v>1163438</v>
       </c>
-      <c r="E2" s="16" t="n">
+      <c r="E2" s="17" t="n">
         <v>1206251</v>
       </c>
-      <c r="F2" s="16" t="n">
+      <c r="F2" s="17" t="n">
         <v>1117170</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Andre driftsindtægter</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n">
+      <c r="B3" s="17" t="n">
         <v>28314</v>
       </c>
-      <c r="C3" s="16" t="n">
+      <c r="C3" s="17" t="n">
         <v>8092</v>
       </c>
-      <c r="D3" s="16" t="n">
+      <c r="D3" s="17" t="n">
         <v>2125</v>
       </c>
-      <c r="E3" s="16" t="n">
+      <c r="E3" s="17" t="n">
         <v>6209</v>
       </c>
-      <c r="F3" s="16" t="n">
+      <c r="F3" s="17" t="n">
         <v>7382</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Vareforbrug</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n">
+      <c r="B4" s="17" t="n">
         <v>-19465</v>
       </c>
-      <c r="C4" s="16" t="n">
+      <c r="C4" s="17" t="n">
         <v>5485</v>
       </c>
-      <c r="D4" s="16" t="n">
+      <c r="D4" s="17" t="n">
         <v>5338</v>
       </c>
-      <c r="E4" s="16" t="n">
+      <c r="E4" s="17" t="n">
         <v>9345</v>
       </c>
-      <c r="F4" s="16" t="n">
+      <c r="F4" s="17" t="n">
         <v>-27072</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Andre eksterne omkostninger</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
+      <c r="B5" s="17" t="n">
         <v>167793</v>
       </c>
-      <c r="C5" s="16" t="n">
+      <c r="C5" s="17" t="n">
         <v>198109</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="D5" s="17" t="n">
         <v>227501</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="E5" s="17" t="n">
         <v>234577</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="F5" s="17" t="n">
         <v>237019</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>Bruttoresultat</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="17" t="n">
         <v>358098</v>
       </c>
-      <c r="C6" s="16" t="n">
+      <c r="C6" s="17" t="n">
         <v>419993</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="D6" s="17" t="n">
         <v>427505</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="E6" s="17" t="n">
         <v>446207</v>
       </c>
-      <c r="F6" s="16" t="n">
+      <c r="F6" s="17" t="n">
         <v>433126</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Personaleomkostninger</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="17" t="n">
         <v>311001</v>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="17" t="n">
         <v>334555</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="D7" s="17" t="n">
         <v>303417</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="E7" s="17" t="n">
         <v>317166</v>
       </c>
-      <c r="F7" s="16" t="n">
+      <c r="F7" s="17" t="n">
         <v>336217</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>Resultat før afskrivninger</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Af- og nedskrivninger</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="17" t="n">
         <v>71169</v>
       </c>
-      <c r="C9" s="16" t="n">
+      <c r="C9" s="17" t="n">
         <v>69425</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="D9" s="17" t="n">
         <v>65798</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="E9" s="17" t="n">
         <v>64117</v>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="F9" s="17" t="n">
         <v>64058</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Andre driftsomkostninger</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" s="17" t="n">
         <v>319</v>
       </c>
-      <c r="C10" s="16" t="n">
+      <c r="C10" s="17" t="n">
         <v>4394</v>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="D10" s="17" t="n">
         <v>3406</v>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="E10" s="17" t="n">
         <v>1319</v>
       </c>
-      <c r="F10" s="16" t="n">
+      <c r="F10" s="17" t="n">
         <v>3699</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Resultat af primær drift</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="17" t="n">
         <v>13970</v>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="17" t="n">
         <v>19711</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <v>57009</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>69814</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="F11" s="17" t="n">
         <v>36534</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Indtægter af kapitalandele, dattervirksomheder</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="17" t="n">
         <v>34921</v>
       </c>
-      <c r="C12" s="16" t="n">
+      <c r="C12" s="17" t="n">
         <v>7689</v>
       </c>
-      <c r="D12" s="16" t="n"/>
-      <c r="E12" s="16" t="n"/>
-      <c r="F12" s="16" t="n"/>
+      <c r="D12" s="17" t="n"/>
+      <c r="E12" s="17" t="n"/>
+      <c r="F12" s="17" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Finansielle indtægter</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
+      <c r="B13" s="17" t="n">
         <v>501</v>
       </c>
-      <c r="C13" s="16" t="n">
+      <c r="C13" s="17" t="n">
         <v>1142</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="17" t="n">
         <v>184</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="E13" s="17" t="n">
         <v>2094</v>
       </c>
-      <c r="F13" s="16" t="n">
+      <c r="F13" s="17" t="n">
         <v>1648</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>Finansielle omkostninger</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
+      <c r="B14" s="17" t="n">
         <v>7066</v>
       </c>
-      <c r="C14" s="16" t="n">
+      <c r="C14" s="17" t="n">
         <v>7309</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="D14" s="17" t="n">
         <v>6232</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="E14" s="17" t="n">
         <v>8737</v>
       </c>
-      <c r="F14" s="16" t="n">
+      <c r="F14" s="17" t="n">
         <v>9703</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>Finansielle poster, netto</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
+      <c r="B15" s="17" t="n">
         <v>-7000</v>
       </c>
-      <c r="C15" s="16" t="n">
+      <c r="C15" s="17" t="n">
         <v>-7000</v>
       </c>
-      <c r="D15" s="16" t="n">
+      <c r="D15" s="17" t="n">
         <v>-7000</v>
       </c>
-      <c r="E15" s="16" t="n"/>
-      <c r="F15" s="16" t="n"/>
+      <c r="E15" s="17" t="n"/>
+      <c r="F15" s="17" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Resultat før skat</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
+      <c r="B16" s="17" t="n">
         <v>6684</v>
       </c>
-      <c r="C16" s="16" t="n">
+      <c r="C16" s="17" t="n">
         <v>12782</v>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="D16" s="17" t="n">
         <v>50344</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="E16" s="17" t="n">
         <v>61886</v>
       </c>
-      <c r="F16" s="16" t="n">
+      <c r="F16" s="17" t="n">
         <v>28683</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Skat af årets resultat</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n">
+      <c r="B17" s="17" t="n">
         <v>6118</v>
       </c>
-      <c r="C17" s="16" t="n">
+      <c r="C17" s="17" t="n">
         <v>15200</v>
       </c>
-      <c r="D17" s="16" t="n">
+      <c r="D17" s="17" t="n">
         <v>12699</v>
       </c>
-      <c r="E17" s="16" t="n">
+      <c r="E17" s="17" t="n">
         <v>18618</v>
       </c>
-      <c r="F17" s="16" t="n">
+      <c r="F17" s="17" t="n">
         <v>10284</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>Årets resultat</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
+      <c r="B18" s="17" t="n">
         <v>566</v>
       </c>
-      <c r="C18" s="16" t="n">
+      <c r="C18" s="17" t="n">
         <v>-2418</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="D18" s="17" t="n">
         <v>37645</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="E18" s="17" t="n">
         <v>43268</v>
       </c>
-      <c r="F18" s="16" t="n">
+      <c r="F18" s="17" t="n">
         <v>18399</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Gns. antal medarbejdere</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n">
+      <c r="B19" s="17" t="n">
         <v>616</v>
       </c>
-      <c r="C19" s="16" t="n">
+      <c r="C19" s="17" t="n">
         <v>587</v>
       </c>
-      <c r="D19" s="16" t="n">
+      <c r="D19" s="17" t="n">
         <v>578</v>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="E19" s="17" t="n">
         <v>605</v>
       </c>
-      <c r="F19" s="16" t="n">
+      <c r="F19" s="17" t="n">
         <v>555</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Investering i materielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n">
+      <c r="B20" s="17" t="n">
         <v>12000</v>
       </c>
-      <c r="C20" s="16" t="n">
+      <c r="C20" s="17" t="n">
         <v>20000</v>
       </c>
-      <c r="D20" s="16" t="n">
+      <c r="D20" s="17" t="n">
         <v>31000</v>
       </c>
-      <c r="E20" s="16" t="n"/>
-      <c r="F20" s="16" t="n"/>
+      <c r="E20" s="17" t="n"/>
+      <c r="F20" s="17" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5203,1072 +5346,1072 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Udviklingsprojekter</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n">
+      <c r="B2" s="17" t="n">
         <v>40291</v>
       </c>
-      <c r="C2" s="16" t="n">
+      <c r="C2" s="17" t="n">
         <v>33782</v>
       </c>
-      <c r="D2" s="16" t="n">
+      <c r="D2" s="17" t="n">
         <v>29009</v>
       </c>
-      <c r="E2" s="16" t="n">
+      <c r="E2" s="17" t="n">
         <v>21264</v>
       </c>
-      <c r="F2" s="16" t="n">
+      <c r="F2" s="17" t="n">
         <v>20875</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Patenter, varemærker mv.</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n">
+      <c r="B3" s="17" t="n">
         <v>1831</v>
       </c>
-      <c r="C3" s="16" t="n">
+      <c r="C3" s="17" t="n">
         <v>3646</v>
       </c>
-      <c r="D3" s="16" t="n"/>
-      <c r="E3" s="16" t="n">
+      <c r="D3" s="17" t="n"/>
+      <c r="E3" s="17" t="n">
         <v>312</v>
       </c>
-      <c r="F3" s="16" t="n">
+      <c r="F3" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Goodwill</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n">
+      <c r="B4" s="17" t="n">
         <v>69050</v>
       </c>
-      <c r="C4" s="16" t="n">
+      <c r="C4" s="17" t="n">
         <v>56069</v>
       </c>
-      <c r="D4" s="16" t="n">
+      <c r="D4" s="17" t="n">
         <v>43088</v>
       </c>
-      <c r="E4" s="16" t="n">
+      <c r="E4" s="17" t="n">
         <v>30106</v>
       </c>
-      <c r="F4" s="16" t="n">
+      <c r="F4" s="17" t="n">
         <v>17125</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>Immaterielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
+      <c r="B5" s="17" t="n">
         <v>112386</v>
       </c>
-      <c r="C5" s="16" t="n">
+      <c r="C5" s="17" t="n">
         <v>94355</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="D5" s="17" t="n">
         <v>75320</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="E5" s="17" t="n">
         <v>52519</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="F5" s="17" t="n">
         <v>38938</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Grunde og bygninger</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="17" t="n">
         <v>219538</v>
       </c>
-      <c r="C6" s="16" t="n">
+      <c r="C6" s="17" t="n">
         <v>208891</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="D6" s="17" t="n">
         <v>199143</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="E6" s="17" t="n">
         <v>214514</v>
       </c>
-      <c r="F6" s="16" t="n">
+      <c r="F6" s="17" t="n">
         <v>236069</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Produktionsanlæg og maskiner</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="17" t="n">
         <v>153962</v>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="17" t="n">
         <v>123350</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="D7" s="17" t="n">
         <v>102604</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="E7" s="17" t="n">
         <v>100519</v>
       </c>
-      <c r="F7" s="16" t="n">
+      <c r="F7" s="17" t="n">
         <v>92065</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Driftsmateriel og inventar</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="17" t="n">
         <v>23965</v>
       </c>
-      <c r="C8" s="16" t="n">
+      <c r="C8" s="17" t="n">
         <v>19898</v>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="D8" s="17" t="n">
         <v>16311</v>
       </c>
-      <c r="E8" s="16" t="n">
+      <c r="E8" s="17" t="n">
         <v>21007</v>
       </c>
-      <c r="F8" s="16" t="n">
+      <c r="F8" s="17" t="n">
         <v>22237</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Indretning af lejede lokaler</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n"/>
-      <c r="C9" s="16" t="n"/>
-      <c r="D9" s="16" t="n"/>
-      <c r="E9" s="16" t="n"/>
-      <c r="F9" s="16" t="n"/>
+      <c r="B9" s="17" t="n"/>
+      <c r="C9" s="17" t="n"/>
+      <c r="D9" s="17" t="n"/>
+      <c r="E9" s="17" t="n"/>
+      <c r="F9" s="17" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Forudbetaling og anlægsaktiver under opførelse</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" s="17" t="n">
         <v>8543</v>
       </c>
-      <c r="C10" s="16" t="n">
+      <c r="C10" s="17" t="n">
         <v>20132</v>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="D10" s="17" t="n">
         <v>37548</v>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="E10" s="17" t="n">
         <v>34058</v>
       </c>
-      <c r="F10" s="16" t="n">
+      <c r="F10" s="17" t="n">
         <v>5313</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Materielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="17" t="n">
         <v>406008</v>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="17" t="n">
         <v>372271</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <v>355606</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>370099</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="F11" s="17" t="n">
         <v>355684</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Kapitalandele, dattervirksomheder</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="17" t="n">
         <v>24267</v>
       </c>
-      <c r="C12" s="16" t="n">
+      <c r="C12" s="17" t="n">
         <v>23504</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="17" t="n">
         <v>22887</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="E12" s="17" t="n">
         <v>21602</v>
       </c>
-      <c r="F12" s="16" t="n">
+      <c r="F12" s="17" t="n">
         <v>21805</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Deposita</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n"/>
-      <c r="C13" s="16" t="n"/>
-      <c r="D13" s="16" t="n"/>
-      <c r="E13" s="16" t="n"/>
-      <c r="F13" s="16" t="n"/>
+      <c r="B13" s="17" t="n"/>
+      <c r="C13" s="17" t="n"/>
+      <c r="D13" s="17" t="n"/>
+      <c r="E13" s="17" t="n"/>
+      <c r="F13" s="17" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>Finansielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
+      <c r="B14" s="17" t="n">
         <v>24267</v>
       </c>
-      <c r="C14" s="16" t="n">
+      <c r="C14" s="17" t="n">
         <v>23504</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="D14" s="17" t="n">
         <v>22887</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="E14" s="17" t="n">
         <v>21602</v>
       </c>
-      <c r="F14" s="16" t="n">
+      <c r="F14" s="17" t="n">
         <v>21805</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>Anlægsaktiver</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
+      <c r="B15" s="17" t="n">
         <v>542661</v>
       </c>
-      <c r="C15" s="16" t="n">
+      <c r="C15" s="17" t="n">
         <v>490130</v>
       </c>
-      <c r="D15" s="16" t="n">
+      <c r="D15" s="17" t="n">
         <v>453813</v>
       </c>
-      <c r="E15" s="16" t="n">
+      <c r="E15" s="17" t="n">
         <v>444220</v>
       </c>
-      <c r="F15" s="16" t="n">
+      <c r="F15" s="17" t="n">
         <v>416427</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>Råvarer og hjælpematerialer</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
+      <c r="B16" s="17" t="n">
         <v>108315</v>
       </c>
-      <c r="C16" s="16" t="n">
+      <c r="C16" s="17" t="n">
         <v>118521</v>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="D16" s="17" t="n">
         <v>118870</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="E16" s="17" t="n">
         <v>110944</v>
       </c>
-      <c r="F16" s="16" t="n">
+      <c r="F16" s="17" t="n">
         <v>107894</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Varer under fremstilling</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n">
+      <c r="B17" s="17" t="n">
         <v>56100</v>
       </c>
-      <c r="C17" s="16" t="n">
+      <c r="C17" s="17" t="n">
         <v>57877</v>
       </c>
-      <c r="D17" s="16" t="n">
+      <c r="D17" s="17" t="n">
         <v>64788</v>
       </c>
-      <c r="E17" s="16" t="n">
+      <c r="E17" s="17" t="n">
         <v>59925</v>
       </c>
-      <c r="F17" s="16" t="n">
+      <c r="F17" s="17" t="n">
         <v>56861</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Færdigvarer og handelsvarer</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
+      <c r="B18" s="17" t="n">
         <v>111955</v>
       </c>
-      <c r="C18" s="16" t="n">
+      <c r="C18" s="17" t="n">
         <v>115663</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="D18" s="17" t="n">
         <v>114090</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="E18" s="17" t="n">
         <v>128299</v>
       </c>
-      <c r="F18" s="16" t="n">
+      <c r="F18" s="17" t="n">
         <v>158434</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Varebeholdninger</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n">
+      <c r="B19" s="17" t="n">
         <v>276370</v>
       </c>
-      <c r="C19" s="16" t="n">
+      <c r="C19" s="17" t="n">
         <v>292061</v>
       </c>
-      <c r="D19" s="16" t="n">
+      <c r="D19" s="17" t="n">
         <v>297748</v>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="E19" s="17" t="n">
         <v>299167</v>
       </c>
-      <c r="F19" s="16" t="n">
+      <c r="F19" s="17" t="n">
         <v>323189</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavender fra salg og tjenesteydelser</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n">
+      <c r="B20" s="17" t="n">
         <v>111880</v>
       </c>
-      <c r="C20" s="16" t="n">
+      <c r="C20" s="17" t="n">
         <v>123931</v>
       </c>
-      <c r="D20" s="16" t="n">
+      <c r="D20" s="17" t="n">
         <v>144078</v>
       </c>
-      <c r="E20" s="16" t="n">
+      <c r="E20" s="17" t="n">
         <v>155320</v>
       </c>
-      <c r="F20" s="16" t="n">
+      <c r="F20" s="17" t="n">
         <v>127243</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavender hos tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B21" s="16" t="n">
+      <c r="B21" s="17" t="n">
         <v>39909</v>
       </c>
-      <c r="C21" s="16" t="n">
+      <c r="C21" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="D21" s="16" t="n"/>
-      <c r="E21" s="16" t="n"/>
-      <c r="F21" s="16" t="n"/>
+      <c r="D21" s="17" t="n"/>
+      <c r="E21" s="17" t="n"/>
+      <c r="F21" s="17" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>Andre tilgodehavender</t>
         </is>
       </c>
-      <c r="B22" s="16" t="n">
+      <c r="B22" s="17" t="n">
         <v>18777</v>
       </c>
-      <c r="C22" s="16" t="n">
+      <c r="C22" s="17" t="n">
         <v>12136</v>
       </c>
-      <c r="D22" s="16" t="n">
+      <c r="D22" s="17" t="n">
         <v>8648</v>
       </c>
-      <c r="E22" s="16" t="n">
+      <c r="E22" s="17" t="n">
         <v>17386</v>
       </c>
-      <c r="F22" s="16" t="n">
+      <c r="F22" s="17" t="n">
         <v>15701</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="inlineStr">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>Periodeafgrænsningsposter (aktiver)</t>
         </is>
       </c>
-      <c r="B23" s="16" t="n">
+      <c r="B23" s="17" t="n">
         <v>13669</v>
       </c>
-      <c r="C23" s="16" t="n">
+      <c r="C23" s="17" t="n">
         <v>21021</v>
       </c>
-      <c r="D23" s="16" t="n">
+      <c r="D23" s="17" t="n">
         <v>18014</v>
       </c>
-      <c r="E23" s="16" t="n">
+      <c r="E23" s="17" t="n">
         <v>15594</v>
       </c>
-      <c r="F23" s="16" t="n">
+      <c r="F23" s="17" t="n">
         <v>18341</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="15" t="inlineStr">
+      <c r="A24" s="16" t="inlineStr">
         <is>
           <t>Udskudt skatteaktiv</t>
         </is>
       </c>
-      <c r="B24" s="16" t="n"/>
-      <c r="C24" s="16" t="n"/>
-      <c r="D24" s="16" t="n"/>
-      <c r="E24" s="16" t="n"/>
-      <c r="F24" s="16" t="n"/>
+      <c r="B24" s="17" t="n"/>
+      <c r="C24" s="17" t="n"/>
+      <c r="D24" s="17" t="n"/>
+      <c r="E24" s="17" t="n"/>
+      <c r="F24" s="17" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavende skat hos tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B25" s="16" t="n"/>
-      <c r="C25" s="16" t="n"/>
-      <c r="D25" s="16" t="n"/>
-      <c r="E25" s="16" t="n"/>
-      <c r="F25" s="16" t="n"/>
+      <c r="B25" s="17" t="n"/>
+      <c r="C25" s="17" t="n"/>
+      <c r="D25" s="17" t="n"/>
+      <c r="E25" s="17" t="n"/>
+      <c r="F25" s="17" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="inlineStr">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>Kortfristede skattetilgodehavender</t>
         </is>
       </c>
-      <c r="B26" s="16" t="n"/>
-      <c r="C26" s="16" t="n"/>
-      <c r="D26" s="16" t="n"/>
-      <c r="E26" s="16" t="n"/>
-      <c r="F26" s="16" t="n"/>
+      <c r="B26" s="17" t="n"/>
+      <c r="C26" s="17" t="n"/>
+      <c r="D26" s="17" t="n"/>
+      <c r="E26" s="17" t="n"/>
+      <c r="F26" s="17" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="17" t="inlineStr">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t>Tilgodehavender</t>
         </is>
       </c>
-      <c r="B27" s="16" t="n">
+      <c r="B27" s="17" t="n">
         <v>144326</v>
       </c>
-      <c r="C27" s="16" t="n">
+      <c r="C27" s="17" t="n">
         <v>157088</v>
       </c>
-      <c r="D27" s="16" t="n">
+      <c r="D27" s="17" t="n">
         <v>170740</v>
       </c>
-      <c r="E27" s="16" t="n">
+      <c r="E27" s="17" t="n">
         <v>188300</v>
       </c>
-      <c r="F27" s="16" t="n">
+      <c r="F27" s="17" t="n">
         <v>162212</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="A28" s="16" t="inlineStr">
         <is>
           <t>Værdipapirer</t>
         </is>
       </c>
-      <c r="B28" s="16" t="n"/>
-      <c r="C28" s="16" t="n"/>
-      <c r="D28" s="16" t="n"/>
-      <c r="E28" s="16" t="n"/>
-      <c r="F28" s="16" t="n"/>
+      <c r="B28" s="17" t="n"/>
+      <c r="C28" s="17" t="n"/>
+      <c r="D28" s="17" t="n"/>
+      <c r="E28" s="17" t="n"/>
+      <c r="F28" s="17" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t>Likvide beholdninger</t>
         </is>
       </c>
-      <c r="B29" s="16" t="n">
+      <c r="B29" s="17" t="n">
         <v>51026</v>
       </c>
-      <c r="C29" s="16" t="n">
+      <c r="C29" s="17" t="n">
         <v>26170</v>
       </c>
-      <c r="D29" s="16" t="n">
+      <c r="D29" s="17" t="n">
         <v>37671</v>
       </c>
-      <c r="E29" s="16" t="n">
+      <c r="E29" s="17" t="n">
         <v>37005</v>
       </c>
-      <c r="F29" s="16" t="n">
+      <c r="F29" s="17" t="n">
         <v>31983</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="17" t="inlineStr">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t>Omsætningsaktiver</t>
         </is>
       </c>
-      <c r="B30" s="16" t="n">
+      <c r="B30" s="17" t="n">
         <v>471722</v>
       </c>
-      <c r="C30" s="16" t="n">
+      <c r="C30" s="17" t="n">
         <v>475319</v>
       </c>
-      <c r="D30" s="16" t="n">
+      <c r="D30" s="17" t="n">
         <v>506159</v>
       </c>
-      <c r="E30" s="16" t="n">
+      <c r="E30" s="17" t="n">
         <v>524472</v>
       </c>
-      <c r="F30" s="16" t="n">
+      <c r="F30" s="17" t="n">
         <v>517385</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="17" t="inlineStr">
+      <c r="A31" s="15" t="inlineStr">
         <is>
           <t>Aktiver</t>
         </is>
       </c>
-      <c r="B31" s="16" t="n">
+      <c r="B31" s="17" t="n">
         <v>1014383</v>
       </c>
-      <c r="C31" s="16" t="n">
+      <c r="C31" s="17" t="n">
         <v>965449</v>
       </c>
-      <c r="D31" s="16" t="n">
+      <c r="D31" s="17" t="n">
         <v>959972</v>
       </c>
-      <c r="E31" s="16" t="n">
+      <c r="E31" s="17" t="n">
         <v>968693</v>
       </c>
-      <c r="F31" s="16" t="n">
+      <c r="F31" s="17" t="n">
         <v>933811</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="15" t="inlineStr">
+      <c r="A32" s="16" t="inlineStr">
         <is>
           <t>Selskabskapital</t>
         </is>
       </c>
-      <c r="B32" s="16" t="n">
+      <c r="B32" s="17" t="n">
         <v>23852</v>
       </c>
-      <c r="C32" s="16" t="n">
+      <c r="C32" s="17" t="n">
         <v>23852</v>
       </c>
-      <c r="D32" s="16" t="n">
+      <c r="D32" s="17" t="n">
         <v>23852</v>
       </c>
-      <c r="E32" s="16" t="n">
+      <c r="E32" s="17" t="n">
         <v>23852</v>
       </c>
-      <c r="F32" s="16" t="n">
+      <c r="F32" s="17" t="n">
         <v>23852</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="15" t="inlineStr">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>Reserve for nettoopskrivning (indre værdis metode)</t>
         </is>
       </c>
-      <c r="B33" s="16" t="n"/>
-      <c r="C33" s="16" t="n"/>
-      <c r="D33" s="16" t="n"/>
-      <c r="E33" s="16" t="n"/>
-      <c r="F33" s="16" t="n"/>
+      <c r="B33" s="17" t="n"/>
+      <c r="C33" s="17" t="n"/>
+      <c r="D33" s="17" t="n"/>
+      <c r="E33" s="17" t="n"/>
+      <c r="F33" s="17" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="15" t="inlineStr">
+      <c r="A34" s="16" t="inlineStr">
         <is>
           <t>Reserve for udviklingsomkostninger</t>
         </is>
       </c>
-      <c r="B34" s="16" t="n">
+      <c r="B34" s="17" t="n">
         <v>36980</v>
       </c>
-      <c r="C34" s="16" t="n">
+      <c r="C34" s="17" t="n">
         <v>26391</v>
       </c>
-      <c r="D34" s="16" t="n">
+      <c r="D34" s="17" t="n">
         <v>23025</v>
       </c>
-      <c r="E34" s="16" t="n"/>
-      <c r="F34" s="16" t="n"/>
+      <c r="E34" s="17" t="n"/>
+      <c r="F34" s="17" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="15" t="inlineStr">
+      <c r="A35" s="16" t="inlineStr">
         <is>
           <t>Reserve for sikringstransaktioner</t>
         </is>
       </c>
-      <c r="B35" s="16" t="n"/>
-      <c r="C35" s="16" t="n"/>
-      <c r="D35" s="16" t="n"/>
-      <c r="E35" s="16" t="n"/>
-      <c r="F35" s="16" t="n"/>
+      <c r="B35" s="17" t="n"/>
+      <c r="C35" s="17" t="n"/>
+      <c r="D35" s="17" t="n"/>
+      <c r="E35" s="17" t="n"/>
+      <c r="F35" s="17" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="15" t="inlineStr">
+      <c r="A36" s="16" t="inlineStr">
         <is>
           <t>Andre reserver</t>
         </is>
       </c>
-      <c r="B36" s="16" t="n"/>
-      <c r="C36" s="16" t="n"/>
-      <c r="D36" s="16" t="n"/>
-      <c r="E36" s="16" t="n">
+      <c r="B36" s="17" t="n"/>
+      <c r="C36" s="17" t="n"/>
+      <c r="D36" s="17" t="n"/>
+      <c r="E36" s="17" t="n">
         <v>16585</v>
       </c>
-      <c r="F36" s="16" t="n">
+      <c r="F36" s="17" t="n">
         <v>16282</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="15" t="inlineStr">
+      <c r="A37" s="16" t="inlineStr">
         <is>
           <t>Overført resultat</t>
         </is>
       </c>
-      <c r="B37" s="16" t="n">
+      <c r="B37" s="17" t="n">
         <v>408551</v>
       </c>
-      <c r="C37" s="16" t="n">
+      <c r="C37" s="17" t="n">
         <v>396860</v>
       </c>
-      <c r="D37" s="16" t="n">
+      <c r="D37" s="17" t="n">
         <v>416442</v>
       </c>
-      <c r="E37" s="16" t="n">
+      <c r="E37" s="17" t="n">
         <v>435510</v>
       </c>
-      <c r="F37" s="16" t="n">
+      <c r="F37" s="17" t="n">
         <v>439989</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="17" t="inlineStr">
+      <c r="A38" s="15" t="inlineStr">
         <is>
           <t>Egenkapital i alt</t>
         </is>
       </c>
-      <c r="B38" s="16" t="n">
+      <c r="B38" s="17" t="n">
         <v>432403</v>
       </c>
-      <c r="C38" s="16" t="n">
+      <c r="C38" s="17" t="n">
         <v>430712</v>
       </c>
-      <c r="D38" s="16" t="n">
+      <c r="D38" s="17" t="n">
         <v>455294</v>
       </c>
-      <c r="E38" s="16" t="n">
+      <c r="E38" s="17" t="n">
         <v>479362</v>
       </c>
-      <c r="F38" s="16" t="n">
+      <c r="F38" s="17" t="n">
         <v>478841</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="15" t="inlineStr">
+      <c r="A39" s="16" t="inlineStr">
         <is>
           <t>Ansvarlig lånekapital (langfristet)</t>
         </is>
       </c>
-      <c r="B39" s="16" t="n"/>
-      <c r="C39" s="16" t="n"/>
-      <c r="D39" s="16" t="n"/>
-      <c r="E39" s="16" t="n"/>
-      <c r="F39" s="16" t="n"/>
+      <c r="B39" s="17" t="n"/>
+      <c r="C39" s="17" t="n"/>
+      <c r="D39" s="17" t="n"/>
+      <c r="E39" s="17" t="n"/>
+      <c r="F39" s="17" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="15" t="inlineStr">
+      <c r="A40" s="16" t="inlineStr">
         <is>
           <t>Langfristede lån</t>
         </is>
       </c>
-      <c r="B40" s="16" t="n">
+      <c r="B40" s="17" t="n">
         <v>213015</v>
       </c>
-      <c r="C40" s="16" t="n">
+      <c r="C40" s="17" t="n">
         <v>194971</v>
       </c>
-      <c r="D40" s="16" t="n">
+      <c r="D40" s="17" t="n">
         <v>176128</v>
       </c>
-      <c r="E40" s="16" t="n">
+      <c r="E40" s="17" t="n">
         <v>147969</v>
       </c>
-      <c r="F40" s="16" t="n">
+      <c r="F40" s="17" t="n">
         <v>134002</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="15" t="inlineStr">
+      <c r="A41" s="16" t="inlineStr">
         <is>
           <t>Leasingforpligtelser (langfristet)</t>
         </is>
       </c>
-      <c r="B41" s="16" t="n"/>
-      <c r="C41" s="16" t="n"/>
-      <c r="D41" s="16" t="n"/>
-      <c r="E41" s="16" t="n"/>
-      <c r="F41" s="16" t="n"/>
+      <c r="B41" s="17" t="n"/>
+      <c r="C41" s="17" t="n"/>
+      <c r="D41" s="17" t="n"/>
+      <c r="E41" s="17" t="n"/>
+      <c r="F41" s="17" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="15" t="inlineStr">
+      <c r="A42" s="16" t="inlineStr">
         <is>
           <t>Anden gæld (langfristet)</t>
         </is>
       </c>
-      <c r="B42" s="16" t="n">
+      <c r="B42" s="17" t="n">
         <v>17063</v>
       </c>
-      <c r="C42" s="16" t="n">
+      <c r="C42" s="17" t="n">
         <v>16864</v>
       </c>
-      <c r="D42" s="16" t="n"/>
-      <c r="E42" s="16" t="n"/>
-      <c r="F42" s="16" t="n"/>
+      <c r="D42" s="17" t="n"/>
+      <c r="E42" s="17" t="n"/>
+      <c r="F42" s="17" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="17" t="inlineStr">
+      <c r="A43" s="15" t="inlineStr">
         <is>
           <t>Langfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B43" s="16" t="n">
+      <c r="B43" s="17" t="n">
         <v>260783</v>
       </c>
-      <c r="C43" s="16" t="n">
+      <c r="C43" s="17" t="n">
         <v>242353</v>
       </c>
-      <c r="D43" s="16" t="n">
+      <c r="D43" s="17" t="n">
         <v>228065</v>
       </c>
-      <c r="E43" s="16" t="n">
+      <c r="E43" s="17" t="n">
         <v>200037</v>
       </c>
-      <c r="F43" s="16" t="n">
+      <c r="F43" s="17" t="n">
         <v>186317</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="15" t="inlineStr">
+      <c r="A44" s="16" t="inlineStr">
         <is>
           <t>Ansvarlig lånekapital (kortfristet)</t>
         </is>
       </c>
-      <c r="B44" s="16" t="n"/>
-      <c r="C44" s="16" t="n"/>
-      <c r="D44" s="16" t="n"/>
-      <c r="E44" s="16" t="n"/>
-      <c r="F44" s="16" t="n"/>
+      <c r="B44" s="17" t="n"/>
+      <c r="C44" s="17" t="n"/>
+      <c r="D44" s="17" t="n"/>
+      <c r="E44" s="17" t="n"/>
+      <c r="F44" s="17" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="15" t="inlineStr">
+      <c r="A45" s="16" t="inlineStr">
         <is>
           <t>Kortfristet del af langfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B45" s="16" t="n"/>
-      <c r="C45" s="16" t="n"/>
-      <c r="D45" s="16" t="n"/>
-      <c r="E45" s="16" t="n"/>
-      <c r="F45" s="16" t="n"/>
+      <c r="B45" s="17" t="n"/>
+      <c r="C45" s="17" t="n"/>
+      <c r="D45" s="17" t="n"/>
+      <c r="E45" s="17" t="n"/>
+      <c r="F45" s="17" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="15" t="inlineStr">
+      <c r="A46" s="16" t="inlineStr">
         <is>
           <t>Kreditinstitutter</t>
         </is>
       </c>
-      <c r="B46" s="16" t="n">
+      <c r="B46" s="17" t="n">
         <v>29101</v>
       </c>
-      <c r="C46" s="16" t="n">
+      <c r="C46" s="17" t="n">
         <v>66770</v>
       </c>
-      <c r="D46" s="16" t="n">
+      <c r="D46" s="17" t="n">
         <v>45255</v>
       </c>
-      <c r="E46" s="16" t="n">
+      <c r="E46" s="17" t="n">
         <v>56632</v>
       </c>
-      <c r="F46" s="16" t="n">
+      <c r="F46" s="17" t="n">
         <v>81281</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="15" t="inlineStr">
+      <c r="A47" s="16" t="inlineStr">
         <is>
           <t>Leasingforpligtelser (kortfristet)</t>
         </is>
       </c>
-      <c r="B47" s="16" t="n"/>
-      <c r="C47" s="16" t="n"/>
-      <c r="D47" s="16" t="n"/>
-      <c r="E47" s="16" t="n"/>
-      <c r="F47" s="16" t="n"/>
+      <c r="B47" s="17" t="n"/>
+      <c r="C47" s="17" t="n"/>
+      <c r="D47" s="17" t="n"/>
+      <c r="E47" s="17" t="n"/>
+      <c r="F47" s="17" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="15" t="inlineStr">
+      <c r="A48" s="16" t="inlineStr">
         <is>
           <t>Leverandører af varer og tjenesteydelser</t>
         </is>
       </c>
-      <c r="B48" s="16" t="n">
+      <c r="B48" s="17" t="n">
         <v>66776</v>
       </c>
-      <c r="C48" s="16" t="n">
+      <c r="C48" s="17" t="n">
         <v>98166</v>
       </c>
-      <c r="D48" s="16" t="n">
+      <c r="D48" s="17" t="n">
         <v>107158</v>
       </c>
-      <c r="E48" s="16" t="n">
+      <c r="E48" s="17" t="n">
         <v>111823</v>
       </c>
-      <c r="F48" s="16" t="n">
+      <c r="F48" s="17" t="n">
         <v>96067</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="15" t="inlineStr">
+      <c r="A49" s="16" t="inlineStr">
         <is>
           <t>Gæld til tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B49" s="16" t="n">
+      <c r="B49" s="17" t="n">
         <v>163003</v>
       </c>
-      <c r="C49" s="16" t="n">
+      <c r="C49" s="17" t="n">
         <v>182575</v>
       </c>
-      <c r="D49" s="16" t="n"/>
-      <c r="E49" s="16" t="n">
+      <c r="D49" s="17" t="n"/>
+      <c r="E49" s="17" t="n">
         <v>163513</v>
       </c>
-      <c r="F49" s="16" t="n">
+      <c r="F49" s="17" t="n">
         <v>153558</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="15" t="inlineStr">
+      <c r="A50" s="16" t="inlineStr">
         <is>
           <t>Gæld til selskabsdeltagere og ledelse</t>
         </is>
       </c>
-      <c r="B50" s="16" t="n">
+      <c r="B50" s="17" t="n">
         <v>10782</v>
       </c>
-      <c r="C50" s="16" t="n">
+      <c r="C50" s="17" t="n">
         <v>6558</v>
       </c>
-      <c r="D50" s="16" t="n">
+      <c r="D50" s="17" t="n">
         <v>23623</v>
       </c>
-      <c r="E50" s="16" t="n">
+      <c r="E50" s="17" t="n">
         <v>2952</v>
       </c>
-      <c r="F50" s="16" t="n">
+      <c r="F50" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="15" t="inlineStr">
+      <c r="A51" s="16" t="inlineStr">
         <is>
           <t>Selskabsskat</t>
         </is>
       </c>
-      <c r="B51" s="16" t="n"/>
-      <c r="C51" s="16" t="n"/>
-      <c r="D51" s="16" t="n"/>
-      <c r="E51" s="16" t="n">
+      <c r="B51" s="17" t="n"/>
+      <c r="C51" s="17" t="n"/>
+      <c r="D51" s="17" t="n"/>
+      <c r="E51" s="17" t="n">
         <v>8587</v>
       </c>
-      <c r="F51" s="16" t="n">
+      <c r="F51" s="17" t="n">
         <v>6502</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="15" t="inlineStr">
+      <c r="A52" s="16" t="inlineStr">
         <is>
           <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
         </is>
       </c>
-      <c r="B52" s="16" t="n">
+      <c r="B52" s="17" t="n">
         <v>5070</v>
       </c>
-      <c r="C52" s="16" t="n">
+      <c r="C52" s="17" t="n">
         <v>4661</v>
       </c>
-      <c r="D52" s="16" t="n">
+      <c r="D52" s="17" t="n">
         <v>634</v>
       </c>
-      <c r="E52" s="16" t="n">
+      <c r="E52" s="17" t="n">
         <v>15204</v>
       </c>
-      <c r="F52" s="16" t="n">
+      <c r="F52" s="17" t="n">
         <v>11011</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="15" t="inlineStr">
+      <c r="A53" s="16" t="inlineStr">
         <is>
           <t>Anden gæld (kortfristet)</t>
         </is>
       </c>
-      <c r="B53" s="16" t="n">
+      <c r="B53" s="17" t="n">
         <v>195742</v>
       </c>
-      <c r="C53" s="16" t="n">
+      <c r="C53" s="17" t="n">
         <v>99053</v>
       </c>
-      <c r="D53" s="16" t="n">
+      <c r="D53" s="17" t="n">
         <v>85995</v>
       </c>
-      <c r="E53" s="16" t="n">
+      <c r="E53" s="17" t="n">
         <v>92420</v>
       </c>
-      <c r="F53" s="16" t="n">
+      <c r="F53" s="17" t="n">
         <v>72513</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="15" t="inlineStr">
+      <c r="A54" s="16" t="inlineStr">
         <is>
           <t>Periodeafgrænsningsposter (passiver)</t>
         </is>
       </c>
-      <c r="B54" s="16" t="n">
+      <c r="B54" s="17" t="n">
         <v>11893</v>
       </c>
-      <c r="C54" s="16" t="n">
+      <c r="C54" s="17" t="n">
         <v>14954</v>
       </c>
-      <c r="D54" s="16" t="n">
+      <c r="D54" s="17" t="n">
         <v>12641</v>
       </c>
-      <c r="E54" s="16" t="n">
+      <c r="E54" s="17" t="n">
         <v>10263</v>
       </c>
-      <c r="F54" s="16" t="n">
+      <c r="F54" s="17" t="n">
         <v>7781</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="17" t="inlineStr">
+      <c r="A55" s="15" t="inlineStr">
         <is>
           <t>Kortfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B55" s="16" t="n">
+      <c r="B55" s="17" t="n">
         <v>321197</v>
       </c>
-      <c r="C55" s="16" t="n">
+      <c r="C55" s="17" t="n">
         <v>292384</v>
       </c>
-      <c r="D55" s="16" t="n">
+      <c r="D55" s="17" t="n">
         <v>276613</v>
       </c>
-      <c r="E55" s="16" t="n">
+      <c r="E55" s="17" t="n">
         <v>289294</v>
       </c>
-      <c r="F55" s="16" t="n">
+      <c r="F55" s="17" t="n">
         <v>268653</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="17" t="inlineStr">
+      <c r="A56" s="15" t="inlineStr">
         <is>
           <t>Gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B56" s="16" t="n">
+      <c r="B56" s="17" t="n">
         <v>581980</v>
       </c>
-      <c r="C56" s="16" t="n">
+      <c r="C56" s="17" t="n">
         <v>534737</v>
       </c>
-      <c r="D56" s="16" t="n">
+      <c r="D56" s="17" t="n">
         <v>504678</v>
       </c>
-      <c r="E56" s="16" t="n">
+      <c r="E56" s="17" t="n">
         <v>489330</v>
       </c>
-      <c r="F56" s="16" t="n">
+      <c r="F56" s="17" t="n">
         <v>454970</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="17" t="inlineStr">
+      <c r="A57" s="15" t="inlineStr">
         <is>
           <t>Passiver</t>
         </is>
       </c>
-      <c r="B57" s="16" t="n">
+      <c r="B57" s="17" t="n">
         <v>1014383</v>
       </c>
-      <c r="C57" s="16" t="n">
+      <c r="C57" s="17" t="n">
         <v>965449</v>
       </c>
-      <c r="D57" s="16" t="n">
+      <c r="D57" s="17" t="n">
         <v>959972</v>
       </c>
-      <c r="E57" s="16" t="n">
+      <c r="E57" s="17" t="n">
         <v>968693</v>
       </c>
-      <c r="F57" s="16" t="n">
+      <c r="F57" s="17" t="n">
         <v>933811</v>
       </c>
     </row>
@@ -6278,6 +6421,128 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="72" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Pengestrømsopgørelse (t.kr.)</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C1" s="3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D1" s="3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E1" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F1" s="3" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra driftsaktivitet</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="n">
+        <v>119269</v>
+      </c>
+      <c r="C2" s="17" t="n">
+        <v>114854</v>
+      </c>
+      <c r="D2" s="17" t="n">
+        <v>89211</v>
+      </c>
+      <c r="E2" s="17" t="n">
+        <v>110318</v>
+      </c>
+      <c r="F2" s="17" t="n">
+        <v>56135</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra investeringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="n">
+        <v>-13031</v>
+      </c>
+      <c r="C3" s="17" t="n">
+        <v>-20491</v>
+      </c>
+      <c r="D3" s="17" t="n">
+        <v>-31890</v>
+      </c>
+      <c r="E3" s="17" t="n">
+        <v>-54290</v>
+      </c>
+      <c r="F3" s="17" t="n">
+        <v>-34917</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra finansieringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="n">
+        <v>-66991</v>
+      </c>
+      <c r="C4" s="17" t="n">
+        <v>-104088</v>
+      </c>
+      <c r="D4" s="17" t="n">
+        <v>-33293</v>
+      </c>
+      <c r="E4" s="17" t="n">
+        <v>-52453</v>
+      </c>
+      <c r="F4" s="17" t="n">
+        <v>-12270</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>Årets pengestrøm</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="n"/>
+      <c r="C5" s="17" t="n"/>
+      <c r="D5" s="17" t="n"/>
+      <c r="E5" s="17" t="n"/>
+      <c r="F5" s="17" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7500,7 +7765,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
